--- a/Result/profitability/7744.xlsx
+++ b/Result/profitability/7744.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1461,24 +1461,24 @@
         <v>528</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F9" t="n">
-        <v>40.77</v>
+        <v>40.94</v>
       </c>
       <c r="G9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>28.95%</t>
+          <t>29.17%</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="J9" t="n">
         <v>125</v>
@@ -1493,7 +1493,7 @@
         <v>3.54875</v>
       </c>
       <c r="N9" t="n">
-        <v>39.76625</v>
+        <v>39.7875</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1526,10 +1526,10 @@
         <v>-0.195</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.510000000000005</v>
+        <v>3.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.09420289855072483</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="AA9" t="n">
         <v>1.53</v>
@@ -1538,10 +1538,10 @@
         <v>0.9053254437869824</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.509999999999998</v>
+        <v>-1.340000000000003</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.0357142857142857</v>
+        <v>-0.03169347209082318</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1588,24 +1588,24 @@
         <v>664</v>
       </c>
       <c r="D10" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E10" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F10" t="n">
-        <v>39.97</v>
+        <v>39.83</v>
       </c>
       <c r="G10" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.51%</t>
+          <t>29.34%</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>205</v>
@@ -1620,7 +1620,7 @@
         <v>3.64625</v>
       </c>
       <c r="N10" t="n">
-        <v>39.95375</v>
+        <v>39.9575</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1653,10 +1653,10 @@
         <v>0.7670807453416149</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.8000000000000043</v>
+        <v>-1.109999999999999</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0196222712779005</v>
+        <v>-0.02711284807034686</v>
       </c>
       <c r="AA10" t="n">
         <v>1.94</v>
@@ -1665,10 +1665,10 @@
         <v>0.5173333333333334</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.769999999999996</v>
+        <v>0.6299999999999955</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01964285714285707</v>
+        <v>0.01607142857142851</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1747,7 +1747,7 @@
         <v>3.3875</v>
       </c>
       <c r="N11" t="n">
-        <v>39.40375</v>
+        <v>39.4075</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1780,10 +1780,10 @@
         <v>-0.3813708260105448</v>
       </c>
       <c r="Y11" t="n">
-        <v>-3.699999999999996</v>
+        <v>-3.559999999999995</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.09256942707030258</v>
+        <v>-0.08937986442380108</v>
       </c>
       <c r="AA11" t="n">
         <v>0.3799999999999999</v>
@@ -1874,7 +1874,7 @@
         <v>3.83375</v>
       </c>
       <c r="N12" t="n">
-        <v>38.49125</v>
+        <v>38.495</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1952,6 +1952,133 @@
       </c>
       <c r="AM12" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7744</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D13" t="n">
+        <v>691</v>
+      </c>
+      <c r="E13" t="n">
+        <v>420</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="G13" t="n">
+        <v>309</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>27.85%</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>31</v>
+      </c>
+      <c r="J13" t="n">
+        <v>341</v>
+      </c>
+      <c r="K13" t="n">
+        <v>250</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="M13" t="n">
+        <v>4.59625</v>
+      </c>
+      <c r="N13" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.3763250883392226</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.710000000000001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.04732908939939118</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.419254658385093</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-3.099999999999994</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.07572056668295057</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
